--- a/test/generator/baseline/gen.ods.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.ods.to.xlsx.xlsx
@@ -20,9 +20,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -54,12 +51,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,8 +562,10 @@
       <c r="C5">
         <v>103</v>
       </c>
-      <c r="D5">
-        <v>7</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7 </t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -605,8 +603,10 @@
       <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8">
-        <v>4</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+4 </t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1278,10 +1278,10 @@
           <t xml:space="preserve">Category 1</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>4.3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>2.4</v>
       </c>
       <c r="F3">
@@ -1294,10 +1294,10 @@
           <t xml:space="preserve">Category 2</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>2.5</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>4.4</v>
       </c>
       <c r="F4">
@@ -1310,10 +1310,10 @@
           <t xml:space="preserve">Category 3</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>3.5</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>1.8</v>
       </c>
       <c r="F5">
@@ -1326,10 +1326,10 @@
           <t xml:space="preserve">Category 4</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>4.5</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>2.8</v>
       </c>
       <c r="F6">

--- a/test/generator/baseline/gen.ods.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.ods.to.xlsx.xlsx
@@ -51,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
     </xf>
@@ -193,14 +194,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Text Formatting </t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Inline formatting </t>
         </is>
@@ -242,7 +243,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fun with fonts </t>
         </is>
@@ -256,7 +257,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Paragraph level formatting </t>
         </is>
@@ -270,7 +271,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">For the lovers of poetry amongst you, paragraphs with hanging indents, like this often
 come in handy. You can use hanging indents to ensure that a line of poetry retains its individual identity as a line even when the screen is  too narrow to display it as a single line. Not only does this paragraph have a hanging indent, it is also has an extra top margin, setting it apart from the preceding paragraph. </t>
@@ -293,19 +294,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tables </t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM </t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">NEEDED </t>
         </is>
@@ -522,22 +523,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">College </t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">New students </t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Graduating students </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Change </t>
         </is>
@@ -895,7 +896,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Structural Elements </t>
         </is>
@@ -909,7 +910,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Footnotes &amp; Endnotes </t>
         </is>
@@ -923,7 +924,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Dropcaps </t>
         </is>
@@ -944,7 +945,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Links </t>
         </is>
@@ -968,7 +969,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Images </t>
         </is>
@@ -1001,7 +1002,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Lists </t>
         </is>
@@ -1015,7 +1016,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bulleted List </t>
         </is>
@@ -1036,7 +1037,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Numbered List </t>
         </is>
@@ -1063,7 +1064,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Multi-level Lists </t>
         </is>
@@ -1172,7 +1173,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Continued Lists </t>
         </is>
@@ -1249,7 +1250,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Charts</t>
         </is>

--- a/test/generator/baseline/gen.ods.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.ods.to.xlsx.xlsx
@@ -982,7 +982,13 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165 Inspirational Quotes To Keep You Motivated In Life</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>

--- a/test/generator/baseline/gen.ods.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.ods.to.xlsx.xlsx
@@ -14,12 +14,16 @@
     <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
     <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
     <sheet name="Chart_Sheet" sheetId="9" r:id="rId9"/>
+    <sheet name="Chart Title" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -51,12 +55,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -184,6 +189,110 @@
       </c>
     </row>
   </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chart Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Series D2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Series E2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Series F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 1</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 2</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 3</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 4</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
 </worksheet>
 </file>
 

--- a/test/generator/baseline/gen.ods.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.ods.to.xlsx.xlsx
@@ -427,8 +427,10 @@
           <t xml:space="preserve">Books </t>
         </is>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -437,8 +439,10 @@
           <t xml:space="preserve">Pens </t>
         </is>
       </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 </t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -447,8 +451,10 @@
           <t xml:space="preserve">Pencils </t>
         </is>
       </c>
-      <c r="B5">
-        <v>2</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -539,8 +545,10 @@
           <t xml:space="preserve">Point B </t>
         </is>
       </c>
-      <c r="B13">
-        <v>87</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87 </t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -554,11 +562,15 @@
           <t xml:space="preserve">Point C </t>
         </is>
       </c>
-      <c r="B14">
-        <v>64</v>
-      </c>
-      <c r="C14">
-        <v>56</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64 </t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56 </t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -572,14 +584,20 @@
           <t xml:space="preserve">Point D </t>
         </is>
       </c>
-      <c r="B15">
-        <v>37</v>
-      </c>
-      <c r="C15">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>91</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37 </t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32 </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91 </t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -593,17 +611,25 @@
           <t xml:space="preserve">Point E </t>
         </is>
       </c>
-      <c r="B16">
-        <v>93</v>
-      </c>
-      <c r="C16">
-        <v>35</v>
-      </c>
-      <c r="D16">
-        <v>54</v>
-      </c>
-      <c r="E16">
-        <v>43</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93 </t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35 </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54 </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43 </t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -666,11 +692,15 @@
           <t xml:space="preserve">Cedar University </t>
         </is>
       </c>
-      <c r="B5">
-        <v>110</v>
-      </c>
-      <c r="C5">
-        <v>103</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110 </t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103 </t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -684,14 +714,20 @@
           <t xml:space="preserve">Oak Institute </t>
         </is>
       </c>
-      <c r="B6">
-        <v>202</v>
-      </c>
-      <c r="C6">
-        <v>210</v>
-      </c>
-      <c r="D6">
-        <v>-8</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202 </t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210 </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-8 </t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -707,11 +743,15 @@
           <t xml:space="preserve">Cedar University </t>
         </is>
       </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 </t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -725,14 +765,20 @@
           <t xml:space="preserve">Elm College </t>
         </is>
       </c>
-      <c r="B9">
-        <v>43</v>
-      </c>
-      <c r="C9">
-        <v>53</v>
-      </c>
-      <c r="D9">
-        <v>-10</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43 </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53 </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10 </t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -741,14 +787,20 @@
           <t xml:space="preserve">Total </t>
         </is>
       </c>
-      <c r="B10">
-        <v>998</v>
-      </c>
-      <c r="C10">
-        <v>908</v>
-      </c>
-      <c r="D10">
-        <v>90</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998 </t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">908 </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90 </t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -870,113 +922,175 @@
       </c>
     </row>
     <row r="5">
-      <c r="M5">
-        <v>1</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 </t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 </t>
+        </is>
       </c>
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>12</v>
-      </c>
-      <c r="I9">
-        <v>13</v>
-      </c>
-      <c r="K9">
-        <v>14</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 </t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 </t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 </t>
+        </is>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>17</v>
-      </c>
-      <c r="E11">
-        <v>18</v>
-      </c>
-      <c r="G11">
-        <v>19</v>
-      </c>
-      <c r="I11">
-        <v>20</v>
-      </c>
-      <c r="K11">
-        <v>21</v>
-      </c>
-      <c r="M11">
-        <v>22</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16 </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17 </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18 </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 </t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21 </t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 </t>
+        </is>
       </c>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13">
-        <v>23</v>
-      </c>
-      <c r="C13">
-        <v>24</v>
-      </c>
-      <c r="E13">
-        <v>25</v>
-      </c>
-      <c r="G13">
-        <v>26</v>
-      </c>
-      <c r="I13">
-        <v>27</v>
-      </c>
-      <c r="K13">
-        <v>28</v>
-      </c>
-      <c r="M13">
-        <v>29</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23 </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25 </t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26 </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27 </t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 </t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29 </t>
+        </is>
       </c>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15">
-        <v>30</v>
-      </c>
-      <c r="C15">
-        <v>31</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 </t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31 </t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1394,10 +1508,10 @@
           <t xml:space="preserve">Category 1</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>4.3</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>2.4</v>
       </c>
       <c r="F3">
@@ -1410,10 +1524,10 @@
           <t xml:space="preserve">Category 2</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>2.5</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>4.4</v>
       </c>
       <c r="F4">
@@ -1426,10 +1540,10 @@
           <t xml:space="preserve">Category 3</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>3.5</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>1.8</v>
       </c>
       <c r="F5">
@@ -1442,10 +1556,10 @@
           <t xml:space="preserve">Category 4</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>4.5</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>2.8</v>
       </c>
       <c r="F6">

--- a/test/generator/baseline/gen.ods.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.ods.to.xlsx.xlsx
@@ -1471,7 +1471,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
